--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.58.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.58.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.58.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.58.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.58.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.58.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0058.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0058.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: answer, is under the following Order : :â€”</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2606 WHITE STAR | isolated marker/symbol line :: ☆</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L6: isolated marker/symbol line :: 2</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,14 +654,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: â˜†</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: answer, is under the following Order :â€”</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: Â»</t>
+          <t>L5: isolated marker/symbol line :: »</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -809,7 +809,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: â˜†</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2606 WHITE STAR | isolated marker/symbol line :: ☆</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -857,7 +857,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
